--- a/data/openbaar/input.xlsx
+++ b/data/openbaar/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln.sharepoint.com/sites/GGD-ONDZ/PSchijf/1 ALGEMEEN ONDERZOEK VRLN/Automatisering/scripts/2026_intern_cbs data/data/openbaar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1403" documentId="13_ncr:1_{1E92AA27-7602-4BE7-AF73-20E1E631BFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BBB6F0A-7787-480C-8633-2CB8D76A371D}"/>
+  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{1E92AA27-7602-4BE7-AF73-20E1E631BFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8DD8CDE-702D-46CD-A925-0103BB3C8E19}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{70528861-4C85-48B7-86A3-D777D99F5CEE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="1" activeTab="5" xr2:uid="{70528861-4C85-48B7-86A3-D777D99F5CEE}"/>
   </bookViews>
   <sheets>
     <sheet name="GGDs (verborgen tabblad)" sheetId="43" state="hidden" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="539">
   <si>
     <t>Onderwerp</t>
   </si>
@@ -442,12 +442,6 @@
     <t>Aantal inwoners, totaal</t>
   </si>
   <si>
-    <t>cbs_kwb_bijstand_perc</t>
-  </si>
-  <si>
-    <t>cbs_kwb_wwuitk_perc</t>
-  </si>
-  <si>
     <t>AfstandTotHuisartsenpraktijk_110</t>
   </si>
   <si>
@@ -526,9 +520,6 @@
     <t>86270NED</t>
   </si>
   <si>
-    <t>AfstandTotOpenbaarGroenTotaal_76</t>
-  </si>
-  <si>
     <t>AfstandTotBibliotheek_92</t>
   </si>
   <si>
@@ -538,12 +529,6 @@
     <t>cbs_kwb_afstandbieb_gem</t>
   </si>
   <si>
-    <t>De gemiddelde afstand van alle inwoners in een gebied tot het dichtstbijzijnde openbaar groen, berekend over de weg</t>
-  </si>
-  <si>
-    <t>cbs_kwb_afstandgroen_gem</t>
-  </si>
-  <si>
     <t>De gemiddelde afstand van alle inwoners in een gebied tot de dichtstbijzijnde huisartsenpraktijk, berekend over de weg</t>
   </si>
   <si>
@@ -556,18 +541,12 @@
     <t>De gemiddelde afstand van alle inwoners in een gebied tot de dichtstbijzijnde school, berekend over de weg</t>
   </si>
   <si>
-    <t>Gemiddelde afstand tot dichtstbijzijnde openbaar groen</t>
-  </si>
-  <si>
     <t>Gemiddelde afstand tot dichtstbijzijnde bibliotheek</t>
   </si>
   <si>
     <t>indicator_includeren</t>
   </si>
   <si>
-    <t>nee</t>
-  </si>
-  <si>
     <t>Burgerlijke staat: Ongehuwd</t>
   </si>
   <si>
@@ -664,12 +643,6 @@
     <t>Personen die een uitkering ontvangen in het kader van de AOW.</t>
   </si>
   <si>
-    <t>cbs_kwb_aouitk_perc</t>
-  </si>
-  <si>
-    <t>cbs_kwb_aowuitk_perc</t>
-  </si>
-  <si>
     <t>SES_wijkenenbuurten_2025</t>
   </si>
   <si>
@@ -721,24 +694,12 @@
     <t>Leeftijd</t>
   </si>
   <si>
-    <t>0 jaar</t>
-  </si>
-  <si>
     <t>Totaal</t>
   </si>
   <si>
-    <t>cbs_bevolkingspyramide_tot</t>
-  </si>
-  <si>
-    <t>cbs_bev_0000_tot</t>
-  </si>
-  <si>
     <t>Totale bevolking op 1 januari</t>
   </si>
   <si>
-    <t>Bevolking met een leeftijd van 0 jaar op 1 januari</t>
-  </si>
-  <si>
     <t>BuitenEuropa_19</t>
   </si>
   <si>
@@ -1045,15 +1006,9 @@
     <t>cbs_part_hh_grootte_gem</t>
   </si>
   <si>
-    <t>cbs_personen_in_part_hh_tot/cbs_kwb_part_hh_tot</t>
-  </si>
-  <si>
     <t>cbs_kwb_bev_0014_perc</t>
   </si>
   <si>
-    <t>cbs_kwb_bev_0014_tot/cbs_kwb_bev_tot</t>
-  </si>
-  <si>
     <t>cbs_kwb_bev_1524_perc</t>
   </si>
   <si>
@@ -1066,18 +1021,6 @@
     <t>cbs_kwb_bev_65eo_perc</t>
   </si>
   <si>
-    <t>cbs_kwb_bev_1524_tot/cbs_kwb_bev_tot</t>
-  </si>
-  <si>
-    <t>cbs_kwb_bev_2544_tot/cbs_kwb_bev_tot</t>
-  </si>
-  <si>
-    <t>cbs_kwb_bev_4564_tot/cbs_kwb_bev_tot</t>
-  </si>
-  <si>
-    <t>cbs_kwb_bev_65eo_tot/cbs_kwb_bev_tot</t>
-  </si>
-  <si>
     <t>unit_Swing</t>
   </si>
   <si>
@@ -1100,6 +1043,657 @@
   </si>
   <si>
     <t>cbs_bevolkingsopbouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_man_tot</t>
+  </si>
+  <si>
+    <t>0 tot 10 jaar</t>
+  </si>
+  <si>
+    <t>dimcat_CategoryGroupID_bewaren</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 0 tot 10 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 0 tot 10 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>BurgerlijkeStaat</t>
+  </si>
+  <si>
+    <t>T001019</t>
+  </si>
+  <si>
+    <t>Totaal burgerlijke staat</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_tot</t>
+  </si>
+  <si>
+    <t>10 tot 20 jaar</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_tot</t>
+  </si>
+  <si>
+    <t>80 tot 90 jaar</t>
+  </si>
+  <si>
+    <t>90 tot 100 jaar</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 10 tot 20 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 20 tot 30 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 30 tot 40 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 40 tot 50 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 50 tot 60 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 60 tot 70 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 70 tot 80 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 80 tot 90 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 90 tot 100 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_vrouw_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 10 tot 20 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 20 tot 30 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 30 tot 40 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 40 tot 50 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 50 tot 60 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 60 tot 70 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 70 tot 80 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 80 tot 90 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 90 tot 100 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 0 tot 10 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 10 tot 20 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 20 tot 30 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 30 tot 40 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 40 tot 50 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 50 tot 60 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 60 tot 70 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 70 tot 80 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 80 tot 90 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 90 tot 100 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_perc</t>
+  </si>
+  <si>
+    <t>(cbs_personen_in_part_hh_tot/cbs_kwb_part_hh_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_kwb_bev_0014_tot/cbs_kwb_bev_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_kwb_bev_1524_tot/cbs_kwb_bev_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_kwb_bev_2544_tot/cbs_kwb_bev_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_kwb_bev_4564_tot/cbs_kwb_bev_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_kwb_bev_65eo_tot/cbs_kwb_bev_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_0009_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_1019_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_2029_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_3039_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_4049_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_5059_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_6069_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_7079_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_8089_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_9099_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_1019_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_3039_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_4049_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_5059_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_6069_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_7079_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_8089_vrouw_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_vrouw_perc</t>
+  </si>
+  <si>
+    <t>(cbs_bev_0009_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_1019_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_2029_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_3039_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_4049_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_5059_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_6069_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_7079_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_8089_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_9099_man_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_0009_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_1019_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_2029_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_3039_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_4049_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_5059_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_6069_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_7079_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_8089_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_9099_vrouw_tot/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_100104_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_105eo_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 100 tot 105 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 105 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_100104_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_105eo_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_100104_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_105eo_vrouw_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 100 tot 105 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 105 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 100 tot 105 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 105 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>100 tot 105 jaar</t>
+  </si>
+  <si>
+    <t>105 jaar of ouder</t>
+  </si>
+  <si>
+    <t>cbs_bev_100eo_vrouw_perc</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_vrouw_tot+cbs_bev_105eo_vrouw_tot)/cbs_bevolkingsopbouw_tot))*100</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 100 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_100eo_man_perc</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 100 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_man_tot+cbs_bev_105eo_man_tot)/cbs_bevolkingsopbouw_tot))*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_100eo_perc</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 100 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_tot+cbs_bev_105eo_tot)/cbs_bevolkingsopbouw_tot))*100</t>
+  </si>
+  <si>
+    <t>Totaal mannen en vrouwen</t>
+  </si>
+  <si>
+    <t>Totaal alle leeftijden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 0 tot 20 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 20 tot 30 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 30 tot 40 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 40 tot 50 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 50 tot 60 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 60 tot 70 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 70 tot 80 jaar dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners van 80 jaar of ouder dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met geslacht man dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met geslacht vrouw dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal ongehuwde inwoners dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal gehuwde inwoners dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal verweduwde inwoners dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Aantal gescheiden inwoners dat door zelfdoding is overleden</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Ophangen/verwurgen</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Medicijnen en/of alcohol</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Voor trein of metro</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Verdrinken</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Springen van hoogte</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Overige wijze van zelfdoding</t>
+  </si>
+  <si>
+    <t>Wijze van zelfdoding: Onbekende wijze van zelfdoding</t>
+  </si>
+  <si>
+    <t>Motief van zelfdoding: Psychische stoornissen</t>
+  </si>
+  <si>
+    <t>Motief van zelfdoding: Fysieke stoornissen</t>
+  </si>
+  <si>
+    <t>Motief van zelfdoding: Huiselijke omstandigheden</t>
+  </si>
+  <si>
+    <t>Motief van zelfdoding: Overig motief van zelfdoding</t>
+  </si>
+  <si>
+    <t>Motief van zelfdoding: Onbekend motief van zelfdoding</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, per 100.000 inwoners</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van ophanging/verwurging</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van medicijnen en/of alcohol</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door voor trein of metro te springen</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van verdrinking</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van springen van hoogte</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van een overige wijze van zelfdoding</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, door middel van een onbekende wijze van zelfdoding</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, met als motief psychische stoornissen</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, met als motief fysieke stoornissen</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, met als motief huiselijke omstandigheden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, met als motief onbekend</t>
+  </si>
+  <si>
+    <t>Aantal inwoners dat door zelfdoding is overleden, met als motief overig</t>
+  </si>
+  <si>
+    <t>cbs_kwb_burgst_ongehuwd_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_burgst_gehuwd_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_burgst_gescheiden_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_burgst_verweduwd_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_part_hh_eenpersoon_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_part_hh_zonderkind_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_part_hh_metkind_tot</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met burgelijke staat ongehuwd</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met burgelijke staat gehuwd</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met burgelijke staat gescheiden</t>
+  </si>
+  <si>
+    <t>Aantal inwoners met burgelijke staat verweduwd</t>
+  </si>
+  <si>
+    <t>Aantal eenpersoonshuishoudens</t>
+  </si>
+  <si>
+    <t>Aantal huishoudens zonder kinderen</t>
+  </si>
+  <si>
+    <t>Aantal huishoudens met kinderen</t>
+  </si>
+  <si>
+    <t>cbs_kwb_bijstand_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_aouitk_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_wwuitk_tot</t>
+  </si>
+  <si>
+    <t>cbs_kwb_aowuitk_tot</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1779,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1209,7 +1803,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1515,138 +2108,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAB6434-861B-4F40-90B2-1A1F61323F23}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1659,18 +2252,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EE835D-AFB6-44E3-8F3D-E90DF98CF0DB}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1694,17 +2287,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BF1EAB-6140-4030-8FDE-B57E5648E132}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,8 +2312,9 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1732,7 +2328,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1746,7 +2342,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1760,7 +2356,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1774,12 +2370,12 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
@@ -1788,7 +2384,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1802,7 +2398,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -1816,7 +2412,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -1830,12 +2426,12 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -1844,40 +2440,40 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D11">
         <v>-99999</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D12">
         <v>-99999</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -1894,22 +2490,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61BD35D-F58D-4CB2-BDC8-136E54518BE6}">
-  <dimension ref="A1:J155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J189"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="7" max="7" width="50.7109375" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="9" width="45.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" customWidth="1"/>
+    <col min="8" max="8" width="74.44140625" customWidth="1"/>
+    <col min="9" max="9" width="45.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1917,16 +2513,16 @@
         <v>49</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>50</v>
@@ -1938,10 +2534,10 @@
         <v>52</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1953,7 +2549,7 @@
       </c>
       <c r="D2" s="3"/>
       <c r="F2" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
@@ -1966,7 +2562,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1978,7 +2574,7 @@
       </c>
       <c r="D3" s="3"/>
       <c r="F3" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>6</v>
@@ -1991,7 +2587,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2003,7 +2599,7 @@
       </c>
       <c r="D4" s="3"/>
       <c r="F4" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -2016,7 +2612,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2029,9 +2625,9 @@
       <c r="D5" s="3"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G5" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -2042,7 +2638,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2057,9 +2653,9 @@
         <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G6" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -2070,37 +2666,37 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>309</v>
+        <v>295</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2113,9 +2709,9 @@
       <c r="D8" s="3"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2126,7 +2722,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2139,9 +2735,9 @@
       <c r="D9" s="3"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -2152,7 +2748,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -2165,9 +2761,9 @@
       <c r="D10" s="3"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G10" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -2178,1613 +2774,2639 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>119</v>
+        <v>295</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>115</v>
+        <v>295</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>116</v>
+        <v>295</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>85</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>97</v>
+        <v>295</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>103</v>
+        <v>295</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>104</v>
+        <v>295</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>105</v>
+        <v>295</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>106</v>
+        <v>295</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>528</v>
+      </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>529</v>
+      </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>530</v>
+      </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>144</v>
+        <v>295</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>141</v>
+        <v>531</v>
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
-      <c r="B24" t="s">
-        <v>140</v>
+      <c r="B24" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="H24" t="s">
+        <v>295</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I24" t="s">
-        <v>142</v>
+      <c r="H24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>146</v>
+        <v>295</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>107</v>
+      <c r="B26" t="s">
+        <v>207</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>316</v>
+        <v>295</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" t="s">
+        <v>141</v>
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>85</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>533</v>
+      </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>85</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>320</v>
+        <v>527</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>317</v>
+        <v>534</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>318</v>
+        <v>534</v>
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>108</v>
+        <v>304</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>108</v>
+        <v>305</v>
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>85</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>122</v>
+        <v>535</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>195</v>
+        <v>536</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>121</v>
+        <v>537</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>85</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>196</v>
+        <v>538</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D36" s="3"/>
       <c r="F36" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D37" s="3"/>
       <c r="F37" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D38" s="3"/>
       <c r="F38" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D39" s="3"/>
       <c r="F39" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" t="s">
         <v>147</v>
       </c>
-      <c r="B40" t="s">
-        <v>149</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D40" s="3"/>
       <c r="F40" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G40" t="s">
+        <v>295</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" t="s">
         <v>154</v>
       </c>
-      <c r="H40" t="s">
-        <v>159</v>
-      </c>
       <c r="I40" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" t="s">
-        <v>150</v>
+        <v>188</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D41" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="F41" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G41" t="s">
-        <v>152</v>
-      </c>
-      <c r="H41" t="s">
-        <v>160</v>
-      </c>
-      <c r="I41" t="s">
-        <v>160</v>
+        <v>295</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>201</v>
+        <v>321</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>320</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>320</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>320</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>320</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>320</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>320</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="H49" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>320</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="C50" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>339</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="H50" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>320</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J44" s="3"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="C51" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>320</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>320</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>320</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>320</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>320</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>320</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>320</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>320</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>320</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>320</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>320</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J71" s="3"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>320</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>320</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="J73" s="3"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J74" s="3"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>320</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J75" s="3"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>320</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>320</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>320</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G79" t="s">
+        <v>256</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" t="s">
+        <v>213</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" t="s">
+        <v>213</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>212</v>
+      </c>
+      <c r="B83" t="s">
+        <v>213</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E83" s="9"/>
+      <c r="F83" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J83" s="3"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>212</v>
+      </c>
+      <c r="B84" t="s">
+        <v>213</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E84" s="9"/>
+      <c r="F84" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J84" s="3"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" t="s">
+        <v>213</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J85" s="3"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J86" s="3"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="J87" s="3"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>212</v>
+      </c>
+      <c r="B88" t="s">
+        <v>213</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J88" s="3"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>212</v>
+      </c>
+      <c r="B89" t="s">
+        <v>213</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J89" s="3"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" t="s">
         <v>225</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C90" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E90" s="9"/>
+      <c r="F90" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J90" s="3"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" t="s">
         <v>226</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C91" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="J91" s="3"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>212</v>
+      </c>
+      <c r="B92" t="s">
         <v>227</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="C92" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="J45" s="3"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" t="s">
-        <v>226</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G46" s="2" t="s">
+      <c r="H92" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J92" s="3"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>212</v>
+      </c>
+      <c r="B93" t="s">
+        <v>228</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>225</v>
-      </c>
-      <c r="B47" t="s">
-        <v>226</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="H93" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="J93" s="3"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B94" t="s">
+        <v>233</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>225</v>
-      </c>
-      <c r="B48" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="H94" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J94" s="3"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95" t="s">
+        <v>234</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="J48" s="3"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>225</v>
-      </c>
-      <c r="B49" t="s">
-        <v>226</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="H95" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="J95" s="3"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" t="s">
+        <v>235</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="J49" s="3"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>225</v>
-      </c>
-      <c r="B50" t="s">
-        <v>226</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="H96" t="s">
+        <v>498</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="J96" s="3"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" t="s">
+        <v>236</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>225</v>
-      </c>
-      <c r="B51" t="s">
-        <v>226</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="H97" t="s">
+        <v>499</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J97" s="3"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="J51" s="3"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>225</v>
-      </c>
-      <c r="B52" t="s">
-        <v>226</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="H98" t="s">
+        <v>500</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="J98" s="3"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>212</v>
+      </c>
+      <c r="B99" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="J52" s="3"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>225</v>
-      </c>
-      <c r="B53" t="s">
-        <v>226</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="H99" t="s">
+        <v>501</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="J99" s="3"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>212</v>
+      </c>
+      <c r="B100" t="s">
+        <v>239</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" t="s">
-        <v>226</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="H100" t="s">
+        <v>502</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J100" s="3"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>212</v>
+      </c>
+      <c r="B101" t="s">
+        <v>247</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="3"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>225</v>
-      </c>
-      <c r="B55" t="s">
-        <v>226</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="H101" t="s">
+        <v>503</v>
+      </c>
+      <c r="I101" t="s">
+        <v>516</v>
+      </c>
+      <c r="J101" s="3"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>212</v>
+      </c>
+      <c r="B102" t="s">
+        <v>248</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>225</v>
-      </c>
-      <c r="B56" t="s">
-        <v>238</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="H102" t="s">
+        <v>504</v>
+      </c>
+      <c r="I102" t="s">
+        <v>517</v>
+      </c>
+      <c r="J102" s="3"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>212</v>
+      </c>
+      <c r="B103" t="s">
+        <v>249</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="J56" s="3"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>225</v>
-      </c>
-      <c r="B57" t="s">
-        <v>239</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="H103" t="s">
+        <v>505</v>
+      </c>
+      <c r="I103" t="s">
+        <v>518</v>
+      </c>
+      <c r="J103" s="3"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" t="s">
+        <v>250</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="J57" s="3"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>225</v>
-      </c>
-      <c r="B58" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="H104" t="s">
+        <v>506</v>
+      </c>
+      <c r="I104" t="s">
+        <v>520</v>
+      </c>
+      <c r="J104" s="3"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>212</v>
+      </c>
+      <c r="B105" t="s">
+        <v>284</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="3"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>225</v>
-      </c>
-      <c r="B59" t="s">
-        <v>241</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="H105" t="s">
+        <v>507</v>
+      </c>
+      <c r="I105" t="s">
+        <v>519</v>
+      </c>
+      <c r="J105" s="3"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" t="s">
         <v>283</v>
       </c>
-      <c r="J59" s="3"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>225</v>
-      </c>
-      <c r="B60" t="s">
-        <v>246</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>225</v>
-      </c>
-      <c r="B61" t="s">
-        <v>247</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J61" s="3"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>225</v>
-      </c>
-      <c r="B62" t="s">
-        <v>248</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="F106" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="J62" s="3"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="J63" s="3"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>225</v>
-      </c>
-      <c r="B64" t="s">
-        <v>250</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J64" s="3"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>225</v>
-      </c>
-      <c r="B65" t="s">
-        <v>251</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J65" s="3"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>225</v>
-      </c>
-      <c r="B66" t="s">
-        <v>252</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J66" s="3"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>225</v>
-      </c>
-      <c r="B67" t="s">
-        <v>260</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="J67" s="3"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>225</v>
-      </c>
-      <c r="B68" t="s">
-        <v>261</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J68" s="3"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>225</v>
-      </c>
-      <c r="B69" t="s">
-        <v>262</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J69" s="3"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>225</v>
-      </c>
-      <c r="B70" t="s">
-        <v>263</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J70" s="3"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>225</v>
-      </c>
-      <c r="B71" t="s">
-        <v>297</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J71" s="3"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>225</v>
-      </c>
-      <c r="B72" t="s">
-        <v>296</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J72" s="3"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J73" s="3"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J74" s="3"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J75" s="3"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J76" s="3"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J77" s="3"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D78" s="9"/>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D79" s="9"/>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D80" s="9"/>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D81" s="9"/>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J83" s="3"/>
-    </row>
-    <row r="84" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J84" s="3"/>
-    </row>
-    <row r="85" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J85" s="3"/>
-    </row>
-    <row r="86" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J86" s="3"/>
-    </row>
-    <row r="87" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J87" s="3"/>
-    </row>
-    <row r="88" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J88" s="3"/>
-    </row>
-    <row r="89" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J89" s="3"/>
-    </row>
-    <row r="90" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J90" s="3"/>
-    </row>
-    <row r="91" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J91" s="3"/>
-    </row>
-    <row r="92" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J92" s="3"/>
-    </row>
-    <row r="93" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J93" s="3"/>
-    </row>
-    <row r="94" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J94" s="3"/>
-    </row>
-    <row r="95" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J95" s="3"/>
-    </row>
-    <row r="96" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J96" s="3"/>
-    </row>
-    <row r="97" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J97" s="3"/>
-    </row>
-    <row r="98" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J98" s="3"/>
-    </row>
-    <row r="99" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J99" s="3"/>
-    </row>
-    <row r="100" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J100" s="3"/>
-    </row>
-    <row r="101" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J101" s="3"/>
-    </row>
-    <row r="102" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J102" s="3"/>
-    </row>
-    <row r="103" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J103" s="3"/>
-    </row>
-    <row r="104" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J104" s="3"/>
-    </row>
-    <row r="105" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J105" s="3"/>
-    </row>
-    <row r="106" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="H106" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>508</v>
+      </c>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F107" s="2"/>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D112" s="9"/>
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D113" s="9"/>
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D114" s="9"/>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D115" s="9"/>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J122" s="3"/>
     </row>
-    <row r="123" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:10" x14ac:dyDescent="0.3">
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J155" s="3"/>
+    </row>
+    <row r="156" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J156" s="3"/>
+    </row>
+    <row r="157" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J157" s="3"/>
+    </row>
+    <row r="158" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J158" s="3"/>
+    </row>
+    <row r="159" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J159" s="3"/>
+    </row>
+    <row r="160" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J160" s="3"/>
+    </row>
+    <row r="161" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J161" s="3"/>
+    </row>
+    <row r="162" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J162" s="3"/>
+    </row>
+    <row r="163" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J163" s="3"/>
+    </row>
+    <row r="164" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J164" s="3"/>
+    </row>
+    <row r="165" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J165" s="3"/>
+    </row>
+    <row r="166" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J166" s="3"/>
+    </row>
+    <row r="167" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J167" s="3"/>
+    </row>
+    <row r="168" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J168" s="3"/>
+    </row>
+    <row r="169" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J169" s="3"/>
+    </row>
+    <row r="170" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J170" s="3"/>
+    </row>
+    <row r="171" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J171" s="3"/>
+    </row>
+    <row r="172" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J172" s="3"/>
+    </row>
+    <row r="173" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J173" s="3"/>
+    </row>
+    <row r="174" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J174" s="3"/>
+    </row>
+    <row r="175" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J175" s="3"/>
+    </row>
+    <row r="176" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J176" s="3"/>
+    </row>
+    <row r="177" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J177" s="3"/>
+    </row>
+    <row r="178" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J178" s="3"/>
+    </row>
+    <row r="179" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J179" s="3"/>
+    </row>
+    <row r="180" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J180" s="3"/>
+    </row>
+    <row r="181" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J181" s="3"/>
+    </row>
+    <row r="182" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J182" s="3"/>
+    </row>
+    <row r="183" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J183" s="3"/>
+    </row>
+    <row r="184" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J184" s="3"/>
+    </row>
+    <row r="185" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J185" s="3"/>
+    </row>
+    <row r="186" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J186" s="3"/>
+    </row>
+    <row r="187" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J187" s="3"/>
+    </row>
+    <row r="188" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J188" s="3"/>
+    </row>
+    <row r="189" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J189" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F627" xr:uid="{937213F6-6876-4084-AFDC-31539A17536A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F661" xr:uid="{937213F6-6876-4084-AFDC-31539A17536A}">
       <formula1>"ja,nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3795,31 +5417,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B971DBA-23FA-4290-8659-12FCAD44EC5E}">
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L175"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -3829,14 +5455,15 @@
       <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D2" s="7"/>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3846,14 +5473,15 @@
       <c r="C3" s="8">
         <v>2016850</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D3" s="8"/>
+      <c r="E3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -3863,44 +5491,47 @@
       <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="C5" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C6" s="8">
         <v>10000</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D6" s="8"/>
+      <c r="E6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -3910,14 +5541,15 @@
       <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D7" s="7"/>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -3927,204 +5559,2484 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D8" s="7"/>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C9" s="8">
         <v>10000</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B11" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B14" t="s">
+        <v>328</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8">
+        <v>7</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" t="s">
+        <v>328</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8">
+        <v>8</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8">
+        <v>9</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B34" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B36" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8">
+        <v>10</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B38" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8">
+        <v>11</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="8">
+        <v>12</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B44" t="s">
+        <v>328</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" s="8">
+        <v>13</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B47" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" s="8">
+        <v>2</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K48" s="8"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B49" t="s">
+        <v>210</v>
+      </c>
+      <c r="C49" s="8">
+        <v>4000</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B50" t="s">
+        <v>328</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K50" s="8"/>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" s="8">
+        <v>3</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B52" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" s="8">
+        <v>4000</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B53" t="s">
+        <v>328</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B54" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" s="8">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B55" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="8">
+        <v>4000</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B56" t="s">
+        <v>328</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B57" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="8">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B59" t="s">
+        <v>328</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" s="8">
+        <v>6</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B62" t="s">
+        <v>328</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+      <c r="D63" s="8">
+        <v>7</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B64" t="s">
+        <v>210</v>
+      </c>
+      <c r="C64" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B65" t="s">
+        <v>328</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B66" t="s">
+        <v>204</v>
+      </c>
+      <c r="D66" s="8">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B68" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="D69" s="8">
+        <v>9</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C70" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B71" t="s">
+        <v>328</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B72" t="s">
+        <v>204</v>
+      </c>
+      <c r="D72" s="8">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B73" t="s">
+        <v>210</v>
+      </c>
+      <c r="C73" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B74" t="s">
+        <v>328</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B75" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="8">
+        <v>11</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B77" t="s">
+        <v>328</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B78" t="s">
+        <v>204</v>
+      </c>
+      <c r="D78" s="8">
+        <v>12</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B79" t="s">
+        <v>210</v>
+      </c>
+      <c r="C79" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B80" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" t="s">
+        <v>204</v>
+      </c>
+      <c r="D81" s="8">
+        <v>13</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B82" t="s">
+        <v>210</v>
+      </c>
+      <c r="C82" s="8">
+        <v>4000</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B83" t="s">
+        <v>328</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B84" t="s">
+        <v>204</v>
+      </c>
+      <c r="D84" s="8">
+        <v>2</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B85" t="s">
+        <v>210</v>
+      </c>
+      <c r="C85" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B86" t="s">
+        <v>328</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B87" t="s">
+        <v>204</v>
+      </c>
+      <c r="D87" s="8">
+        <v>3</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B88" t="s">
+        <v>210</v>
+      </c>
+      <c r="C88" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B89" t="s">
+        <v>328</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B90" t="s">
+        <v>204</v>
+      </c>
+      <c r="D90" s="8">
+        <v>4</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B91" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B92" t="s">
+        <v>328</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B93" t="s">
+        <v>204</v>
+      </c>
+      <c r="D93" s="8">
+        <v>5</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B94" t="s">
+        <v>210</v>
+      </c>
+      <c r="C94" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B95" t="s">
+        <v>328</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B96" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="8">
+        <v>6</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B97" t="s">
+        <v>210</v>
+      </c>
+      <c r="C97" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B98" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B99" t="s">
+        <v>204</v>
+      </c>
+      <c r="D99" s="8">
+        <v>7</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B100" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B101" t="s">
+        <v>328</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B102" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" s="8">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B103" t="s">
+        <v>210</v>
+      </c>
+      <c r="C103" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B104" t="s">
+        <v>328</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B105" t="s">
+        <v>204</v>
+      </c>
+      <c r="D105" s="8">
+        <v>9</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B106" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B107" t="s">
+        <v>328</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B108" t="s">
+        <v>204</v>
+      </c>
+      <c r="D108" s="8">
+        <v>10</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B109" t="s">
+        <v>210</v>
+      </c>
+      <c r="C109" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B110" t="s">
+        <v>328</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B111" t="s">
+        <v>204</v>
+      </c>
+      <c r="D111" s="8">
+        <v>11</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B112" t="s">
+        <v>210</v>
+      </c>
+      <c r="C112" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B113" t="s">
+        <v>328</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B114" t="s">
+        <v>204</v>
+      </c>
+      <c r="D114" s="8">
+        <v>12</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B115" t="s">
+        <v>210</v>
+      </c>
+      <c r="C115" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B116" t="s">
+        <v>328</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B117" t="s">
+        <v>204</v>
+      </c>
+      <c r="D117" s="8">
+        <v>13</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B118" t="s">
+        <v>210</v>
+      </c>
+      <c r="C118" s="8">
+        <v>3000</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B119" t="s">
+        <v>328</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" t="s">
+        <v>204</v>
+      </c>
+      <c r="C120" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>256</v>
+      </c>
+      <c r="B121" t="s">
+        <v>210</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D121" s="8"/>
+      <c r="E121" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B122" t="s">
+        <v>204</v>
+      </c>
+      <c r="C122" s="8">
+        <v>41400</v>
+      </c>
+      <c r="D122" s="8"/>
+      <c r="E122" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="K122" s="8"/>
+      <c r="L122" s="3"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B123" t="s">
+        <v>210</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D123" s="8"/>
+      <c r="E123" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K123" s="8"/>
+      <c r="L123" s="3"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" t="s">
+        <v>204</v>
+      </c>
+      <c r="C124" s="8">
+        <v>60300</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K124" s="8"/>
+      <c r="L124" s="3"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B125" t="s">
+        <v>210</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D125" s="8"/>
+      <c r="E125" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K125" s="8"/>
+      <c r="L125" s="3"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B126" t="s">
+        <v>204</v>
+      </c>
+      <c r="C126" s="8">
+        <v>60400</v>
+      </c>
+      <c r="D126" s="8"/>
+      <c r="E126" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="8">
-        <v>10010</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="K126" s="8"/>
+      <c r="L126" s="3"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B127" t="s">
+        <v>210</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D127" s="8"/>
+      <c r="E127" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K127" s="8"/>
+      <c r="L127" s="3"/>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B128" t="s">
+        <v>204</v>
+      </c>
+      <c r="C128" s="8">
+        <v>60500</v>
+      </c>
+      <c r="D128" s="8"/>
+      <c r="E128" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K128" s="8"/>
+      <c r="L128" s="3"/>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" t="s">
+        <v>210</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D129" s="8"/>
+      <c r="E129" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K129" s="8"/>
+      <c r="L129" s="3"/>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B130" t="s">
+        <v>204</v>
+      </c>
+      <c r="C130" s="8">
+        <v>60600</v>
+      </c>
+      <c r="D130" s="8"/>
+      <c r="E130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K130" s="8"/>
+      <c r="L130" s="3"/>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" t="s">
+        <v>210</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D131" s="8"/>
+      <c r="E131" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K131" s="8"/>
+      <c r="L131" s="3"/>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
+        <v>204</v>
+      </c>
+      <c r="C132" s="8">
+        <v>60700</v>
+      </c>
+      <c r="D132" s="8"/>
+      <c r="E132" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K132" s="8"/>
+      <c r="L132" s="3"/>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B133" t="s">
+        <v>210</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D133" s="8"/>
+      <c r="E133" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K133" s="8"/>
+      <c r="L133" s="3"/>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B134" t="s">
+        <v>204</v>
+      </c>
+      <c r="C134" s="8">
+        <v>60800</v>
+      </c>
+      <c r="D134" s="8"/>
+      <c r="E134" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K134" s="8"/>
+      <c r="L134" s="3"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B135" t="s">
+        <v>210</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D135" s="8"/>
+      <c r="E135" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K135" s="8"/>
+      <c r="L135" s="3"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B136" t="s">
+        <v>204</v>
+      </c>
+      <c r="C136" s="8">
+        <v>21700</v>
+      </c>
+      <c r="D136" s="8"/>
+      <c r="E136" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K136" s="8"/>
+      <c r="L136" s="3"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B137" t="s">
+        <v>210</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D137" s="8"/>
+      <c r="E137" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K137" s="8"/>
+      <c r="L137" s="3"/>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B138" t="s">
+        <v>204</v>
+      </c>
+      <c r="C138" s="8">
+        <v>10000</v>
+      </c>
+      <c r="D138" s="8"/>
+      <c r="E138" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K138" s="8"/>
+      <c r="L138" s="3"/>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B139" t="s">
+        <v>210</v>
+      </c>
+      <c r="C139" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D139" s="8"/>
+      <c r="E139" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K139" s="8"/>
+      <c r="L139" s="3"/>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B140" t="s">
+        <v>204</v>
+      </c>
+      <c r="C140" s="8">
+        <v>10000</v>
+      </c>
+      <c r="D140" s="8"/>
+      <c r="E140" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K140" s="8"/>
+      <c r="L140" s="3"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B141" t="s">
+        <v>210</v>
+      </c>
+      <c r="C141" s="8">
+        <v>4000</v>
+      </c>
+      <c r="D141" s="8"/>
+      <c r="E141" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K141" s="8"/>
+      <c r="L141" s="3"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B142" t="s">
+        <v>204</v>
+      </c>
+      <c r="C142" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" t="s">
+        <v>210</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D143" s="8"/>
+      <c r="E143" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B144" t="s">
+        <v>204</v>
+      </c>
+      <c r="C144" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B145" t="s">
+        <v>210</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D145" s="8"/>
+      <c r="E145" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B146" t="s">
+        <v>204</v>
+      </c>
+      <c r="C146" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B147" t="s">
+        <v>210</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D147" s="8"/>
+      <c r="E147" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="8">
-        <v>41400</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B148" t="s">
+        <v>204</v>
+      </c>
+      <c r="C148" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B149" t="s">
+        <v>210</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="8">
-        <v>60300</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B150" t="s">
+        <v>204</v>
+      </c>
+      <c r="C150" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B151" t="s">
+        <v>210</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D151" s="8"/>
+      <c r="E151" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="8">
-        <v>60400</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B152" t="s">
+        <v>204</v>
+      </c>
+      <c r="C152" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B153" t="s">
+        <v>210</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D153" s="8"/>
+      <c r="E153" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="8">
-        <v>60500</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B154" t="s">
+        <v>204</v>
+      </c>
+      <c r="C154" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B155" t="s">
+        <v>210</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D155" s="8"/>
+      <c r="E155" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" s="8">
-        <v>60600</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B156" t="s">
+        <v>204</v>
+      </c>
+      <c r="C156" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B157" t="s">
+        <v>210</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D157" s="8"/>
+      <c r="E157" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="8">
-        <v>60700</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B158" t="s">
+        <v>204</v>
+      </c>
+      <c r="C158" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B159" t="s">
+        <v>210</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D159" s="8"/>
+      <c r="E159" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="8">
-        <v>60800</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B160" t="s">
+        <v>204</v>
+      </c>
+      <c r="C160" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B161" t="s">
+        <v>210</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D161" s="8"/>
+      <c r="E161" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" s="8">
-        <v>21700</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B162" t="s">
+        <v>204</v>
+      </c>
+      <c r="C162" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B163" t="s">
+        <v>210</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="8">
-        <v>3000</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B164" t="s">
+        <v>204</v>
+      </c>
+      <c r="C164" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B165" t="s">
+        <v>210</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B20" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="8">
-        <v>4000</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="3"/>
+      <c r="B166" t="s">
+        <v>204</v>
+      </c>
+      <c r="C166" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B167" t="s">
+        <v>210</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D167" s="8"/>
+      <c r="E167" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B168" t="s">
+        <v>204</v>
+      </c>
+      <c r="C168" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B169" t="s">
+        <v>210</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D169" s="8"/>
+      <c r="E169" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B170" t="s">
+        <v>204</v>
+      </c>
+      <c r="C170" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B171" t="s">
+        <v>210</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D171" s="8"/>
+      <c r="E171" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B172" t="s">
+        <v>204</v>
+      </c>
+      <c r="C172" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B173" t="s">
+        <v>210</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D173" s="8"/>
+      <c r="E173" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B174" t="s">
+        <v>204</v>
+      </c>
+      <c r="C174" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B175" t="s">
+        <v>210</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D175" s="8"/>
+      <c r="E175" s="3" t="s">
+        <v>479</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4133,17 +8045,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C088605-A26C-4C42-A4E5-A84C862CBB5B}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" customWidth="1"/>
-    <col min="4" max="4" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.88671875" customWidth="1"/>
+    <col min="4" max="4" width="65.88671875" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>50</v>
       </c>
@@ -4154,30 +8067,30 @@
         <v>52</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
         <v>317</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" t="s">
-        <v>336</v>
       </c>
       <c r="F2">
         <v>0.1</v>
@@ -4185,9 +8098,9 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>98</v>
@@ -4196,18 +8109,18 @@
         <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>324</v>
+        <v>401</v>
       </c>
       <c r="E3" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>101</v>
@@ -4216,18 +8129,18 @@
         <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="E4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
@@ -4236,18 +8149,18 @@
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="E5" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>100</v>
@@ -4256,18 +8169,18 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>331</v>
+        <v>404</v>
       </c>
       <c r="E6" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>102</v>
@@ -4276,12 +8189,684 @@
         <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E18" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E21" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E22" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E23" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E25" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E26" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E27" t="s">
+        <v>315</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E28" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" t="s">
+        <v>315</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E33" t="s">
+        <v>315</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E34" t="s">
+        <v>315</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E35" t="s">
+        <v>315</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E36" t="s">
+        <v>315</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E37" t="s">
+        <v>315</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E38" t="s">
+        <v>315</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E39" t="s">
+        <v>315</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E40" t="s">
+        <v>315</v>
+      </c>
+      <c r="F40">
         <v>1</v>
       </c>
     </row>
@@ -4292,6 +8877,22 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4300,7 +8901,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4EA295FB1FB9547A73C9F5819D6E613" ma:contentTypeVersion="23" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fb09b8f9996d29818860aca561f17aea">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4e95bed8-6d15-4403-ad70-a53422338dca" xmlns:ns3="10d3344f-2d16-43d9-a145-97142f5cb288" xmlns:ns4="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f29125cba2118f3064d103e6e0ba85ce" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4585,23 +9186,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B2EDF01-6F7E-4DF9-9F88-B818D2B74C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="0655e6f0-bc5a-4a6f-90a0-f11d05f73b85"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c1decae3-bc71-419f-8045-b4e53679b539"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
+    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8069972A-8AC8-46B4-B83D-A93C29A0EF5A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4609,7 +9214,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34C22BA0-1772-4802-A0A5-1C083BD3B5B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4628,24 +9233,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B2EDF01-6F7E-4DF9-9F88-B818D2B74C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="0655e6f0-bc5a-4a6f-90a0-f11d05f73b85"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c1decae3-bc71-419f-8045-b4e53679b539"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
-    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/openbaar/input.xlsx
+++ b/data/openbaar/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln.sharepoint.com/sites/GGD-ONDZ/PSchijf/1 ALGEMEEN ONDERZOEK VRLN/Automatisering/scripts/2026_intern_cbs data/data/openbaar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln.sharepoint.com/sites/GGD-ONDZ/PSchijf/1 ALGEMEEN ONDERZOEK VRLN/Automatisering/scripts/CBS2Swing/data/openbaar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{1E92AA27-7602-4BE7-AF73-20E1E631BFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8DD8CDE-702D-46CD-A925-0103BB3C8E19}"/>
+  <xr:revisionPtr revIDLastSave="2469" documentId="13_ncr:1_{1E92AA27-7602-4BE7-AF73-20E1E631BFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86B3EAC-1AD8-4921-B604-B770C65567FB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="1" activeTab="5" xr2:uid="{70528861-4C85-48B7-86A3-D777D99F5CEE}"/>
+    <workbookView xWindow="-23148" yWindow="1140" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{70528861-4C85-48B7-86A3-D777D99F5CEE}"/>
   </bookViews>
   <sheets>
     <sheet name="GGDs (verborgen tabblad)" sheetId="43" state="hidden" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="580">
   <si>
     <t>Onderwerp</t>
   </si>
@@ -1492,9 +1492,6 @@
     <t>cbs_bev_100eo_vrouw_perc</t>
   </si>
   <si>
-    <t>((cbs_bev_100104_vrouw_tot+cbs_bev_105eo_vrouw_tot)/cbs_bevolkingsopbouw_tot))*100</t>
-  </si>
-  <si>
     <t>Bevolking met geslacht vrouw met een leeftijd van 100 jaar of ouder op 1 januari</t>
   </si>
   <si>
@@ -1504,18 +1501,12 @@
     <t>Bevolking met geslacht man met een leeftijd van 100 jaar of ouder op 1 januari</t>
   </si>
   <si>
-    <t>((cbs_bev_100104_man_tot+cbs_bev_105eo_man_tot)/cbs_bevolkingsopbouw_tot))*100</t>
-  </si>
-  <si>
     <t>cbs_bev_100eo_perc</t>
   </si>
   <si>
     <t>Bevolking met een leeftijd van 100 jaar of ouder op 1 januari</t>
   </si>
   <si>
-    <t>((cbs_bev_100104_tot+cbs_bev_105eo_tot)/cbs_bevolkingsopbouw_tot))*100</t>
-  </si>
-  <si>
     <t>Totaal mannen en vrouwen</t>
   </si>
   <si>
@@ -1694,6 +1685,138 @@
   </si>
   <si>
     <t>cbs_kwb_aowuitk_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 0 tot 20 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_0019_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_0009_tot + cbs_bev_1019_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_2064_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 20 tot 65 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_6064_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 60 tot 65 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>60 tot 65 jaar</t>
+  </si>
+  <si>
+    <t>cbs_bev_65eo_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_6569_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 65 tot 70 jaar op 1 januari</t>
+  </si>
+  <si>
+    <t>65 tot 70 jaar</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 65 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_2029_tot + cbs_bev_3039_tot + cbs_bev_4049_tot + cbs_bev_5059_tot + cbs_bev_6064_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_6569_tot + cbs_bev_7079_tot + cbs_bev_8089_tot + cbs_bev_9099_tot + cbs_bev_100104_tot + cbs_bev_105eo_tot</t>
+  </si>
+  <si>
+    <t>Grijze druk: Aantal 65-plussers per 100 20-65 jarigen</t>
+  </si>
+  <si>
+    <t>Groene druk: Aantal 0 tot 20-jarigen per 100 20-65 jarigen</t>
+  </si>
+  <si>
+    <t>cbs_bev_groene_druk_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_grijze_druk_perc</t>
+  </si>
+  <si>
+    <t>(cbs_bev_0019_tot/cbs_bev_2064_tot)*100</t>
+  </si>
+  <si>
+    <t>(cbs_bev_65eo_tot/cbs_bev_2064_tot)*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_demografische_druk_perc</t>
+  </si>
+  <si>
+    <t>Demografische druk: Aantal 0 tot 20-jarigen plus het aantal 65-plusser per 100 20-65 jarigen</t>
+  </si>
+  <si>
+    <t>((cbs_bev_0019_tot+cbs_bev_65eo_tot)/cbs_bev_2064_tot)*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_tot</t>
+  </si>
+  <si>
+    <t>Bevolking met een leeftijd van 90 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_tot + cbs_bev_100104_tot + cbs_bev_105eo_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_perc</t>
+  </si>
+  <si>
+    <t>((cbs_bev_9099_tot + cbs_bev_100104_tot + cbs_bev_105eo_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_man_perc</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_vrouw_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_90eo_vrouw_perc</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht man met een leeftijd van 90 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>Bevolking met geslacht vrouw met een leeftijd van 90 jaar of ouder op 1 januari</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_man_tot + cbs_bev_100104_man_tot + cbs_bev_105eo_man_tot</t>
+  </si>
+  <si>
+    <t>cbs_bev_9099_vrouw_tot + cbs_bev_100104_vrouw_tot + cbs_bev_105eo_vrouw_tot</t>
+  </si>
+  <si>
+    <t>((cbs_bev_9099_vrouw_tot + cbs_bev_100104_vrouw_tot + cbs_bev_105eo_vrouw_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>((cbs_bev_9099_man_tot + cbs_bev_100104_man_tot + cbs_bev_105eo_man_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_vrouw_tot+cbs_bev_105eo_vrouw_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_man_tot+cbs_bev_105eo_man_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>((cbs_bev_100104_tot+cbs_bev_105eo_tot)/cbs_bevolkingsopbouw_tot)*100</t>
+  </si>
+  <si>
+    <t>16000,16100,16200,16300,16400</t>
+  </si>
+  <si>
+    <t>16500,16600,16700,16800,16900</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1787,9 +1910,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1802,8 +1922,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2108,138 +2226,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAB6434-861B-4F40-90B2-1A1F61323F23}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -2252,18 +2370,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EE835D-AFB6-44E3-8F3D-E90DF98CF0DB}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -2288,18 +2406,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BF1EAB-6140-4030-8FDE-B57E5648E132}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2432,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2328,7 +2446,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2342,7 +2460,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2356,7 +2474,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2370,7 +2488,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>287</v>
       </c>
@@ -2384,7 +2502,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2398,7 +2516,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -2412,7 +2530,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -2426,7 +2544,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -2440,7 +2558,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>188</v>
       </c>
@@ -2454,7 +2572,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>320</v>
       </c>
@@ -2468,7 +2586,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>212</v>
       </c>
@@ -2490,54 +2608,54 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61BD35D-F58D-4CB2-BDC8-136E54518BE6}">
-  <dimension ref="A1:J189"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J191"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="32.33203125" customWidth="1"/>
-    <col min="8" max="8" width="74.44140625" customWidth="1"/>
-    <col min="9" max="9" width="45.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="32.28515625" customWidth="1"/>
+    <col min="8" max="8" width="74.42578125" customWidth="1"/>
+    <col min="9" max="9" width="45.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2562,7 +2680,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2587,7 +2705,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2612,7 +2730,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2638,7 +2756,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2666,7 +2784,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -2696,7 +2814,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -2722,7 +2840,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2748,7 +2866,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -2774,7 +2892,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -2800,7 +2918,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -2824,7 +2942,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -2850,7 +2968,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -2876,7 +2994,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -2902,7 +3020,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -2928,7 +3046,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -2954,7 +3072,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -2980,7 +3098,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3006,7 +3124,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -3022,17 +3140,17 @@
         <v>295</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -3048,17 +3166,17 @@
         <v>295</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -3074,17 +3192,17 @@
         <v>295</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3100,17 +3218,17 @@
         <v>295</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -3136,7 +3254,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -3162,7 +3280,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -3187,7 +3305,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>85</v>
       </c>
@@ -3213,7 +3331,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -3229,17 +3347,17 @@
         <v>295</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -3255,17 +3373,17 @@
         <v>295</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -3281,17 +3399,17 @@
         <v>295</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>85</v>
       </c>
@@ -3317,7 +3435,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>85</v>
       </c>
@@ -3335,7 +3453,7 @@
         <v>295</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>196</v>
@@ -3345,7 +3463,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -3363,7 +3481,7 @@
         <v>295</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>197</v>
@@ -3373,7 +3491,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3391,7 +3509,7 @@
         <v>295</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>203</v>
@@ -3401,7 +3519,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -3419,7 +3537,7 @@
         <v>295</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>198</v>
@@ -3429,7 +3547,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>85</v>
       </c>
@@ -3454,7 +3572,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -3479,7 +3597,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -3504,7 +3622,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -3529,7 +3647,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>145</v>
       </c>
@@ -3543,7 +3661,7 @@
       <c r="F40" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" t="s">
         <v>149</v>
       </c>
       <c r="H40" t="s">
@@ -3554,7 +3672,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -3581,7 +3699,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>320</v>
       </c>
@@ -3605,7 +3723,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>320</v>
       </c>
@@ -3629,7 +3747,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>320</v>
       </c>
@@ -3653,7 +3771,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>320</v>
       </c>
@@ -3677,7 +3795,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>320</v>
       </c>
@@ -3701,7 +3819,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>320</v>
       </c>
@@ -3725,7 +3843,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>320</v>
       </c>
@@ -3749,7 +3867,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>320</v>
       </c>
@@ -3773,7 +3891,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>320</v>
       </c>
@@ -3797,7 +3915,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>320</v>
       </c>
@@ -3821,7 +3939,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>320</v>
       </c>
@@ -3845,7 +3963,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>320</v>
       </c>
@@ -3869,7 +3987,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>320</v>
       </c>
@@ -3893,7 +4011,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>320</v>
       </c>
@@ -3907,17 +4025,17 @@
         <v>295</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>327</v>
+        <v>542</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>327</v>
+        <v>542</v>
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>320</v>
       </c>
@@ -3931,17 +4049,17 @@
         <v>295</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>352</v>
+        <v>545</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>371</v>
+        <v>546</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>371</v>
+        <v>546</v>
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>320</v>
       </c>
@@ -3955,17 +4073,17 @@
         <v>295</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>320</v>
       </c>
@@ -3979,17 +4097,17 @@
         <v>295</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>320</v>
       </c>
@@ -4003,17 +4121,17 @@
         <v>295</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>320</v>
       </c>
@@ -4027,17 +4145,17 @@
         <v>295</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>320</v>
       </c>
@@ -4051,17 +4169,17 @@
         <v>295</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>320</v>
       </c>
@@ -4075,17 +4193,17 @@
         <v>295</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>320</v>
       </c>
@@ -4099,17 +4217,17 @@
         <v>295</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>320</v>
       </c>
@@ -4123,17 +4241,17 @@
         <v>295</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>320</v>
       </c>
@@ -4147,17 +4265,17 @@
         <v>295</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>320</v>
       </c>
@@ -4171,17 +4289,17 @@
         <v>295</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>461</v>
+        <v>360</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>320</v>
       </c>
@@ -4195,17 +4313,17 @@
         <v>295</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>320</v>
       </c>
@@ -4219,17 +4337,17 @@
         <v>295</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>362</v>
+        <v>461</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>381</v>
+        <v>465</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>381</v>
+        <v>465</v>
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>320</v>
       </c>
@@ -4243,17 +4361,17 @@
         <v>295</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>320</v>
       </c>
@@ -4267,17 +4385,17 @@
         <v>295</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>320</v>
       </c>
@@ -4291,17 +4409,17 @@
         <v>295</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>320</v>
       </c>
@@ -4315,17 +4433,17 @@
         <v>295</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>320</v>
       </c>
@@ -4339,17 +4457,17 @@
         <v>295</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>320</v>
       </c>
@@ -4363,17 +4481,17 @@
         <v>295</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>320</v>
       </c>
@@ -4387,17 +4505,17 @@
         <v>295</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>320</v>
       </c>
@@ -4411,17 +4529,17 @@
         <v>295</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>320</v>
       </c>
@@ -4435,17 +4553,17 @@
         <v>295</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>462</v>
+        <v>369</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>320</v>
       </c>
@@ -4459,66 +4577,65 @@
         <v>295</v>
       </c>
       <c r="G78" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>320</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>320</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H80" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="I78" s="2" t="s">
+      <c r="I80" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>212</v>
-      </c>
-      <c r="B79" t="s">
-        <v>213</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G79" t="s">
-        <v>256</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>212</v>
-      </c>
-      <c r="B80" t="s">
-        <v>213</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>212</v>
       </c>
@@ -4528,22 +4645,21 @@
       <c r="C81" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E81" s="9"/>
       <c r="F81" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>258</v>
+      <c r="G81" t="s">
+        <v>256</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>212</v>
       </c>
@@ -4553,22 +4669,22 @@
       <c r="C82" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E82" s="9"/>
+      <c r="E82" s="8"/>
       <c r="F82" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>212</v>
       </c>
@@ -4578,22 +4694,22 @@
       <c r="C83" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E83" s="9"/>
+      <c r="E83" s="8"/>
       <c r="F83" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>212</v>
       </c>
@@ -4603,22 +4719,22 @@
       <c r="C84" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E84" s="9"/>
+      <c r="E84" s="8"/>
       <c r="F84" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>212</v>
       </c>
@@ -4628,22 +4744,22 @@
       <c r="C85" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E85" s="9"/>
+      <c r="E85" s="8"/>
       <c r="F85" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>212</v>
       </c>
@@ -4653,21 +4769,22 @@
       <c r="C86" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="E86" s="8"/>
       <c r="F86" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>212</v>
       </c>
@@ -4677,21 +4794,22 @@
       <c r="C87" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="E87" s="8"/>
       <c r="F87" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>212</v>
       </c>
@@ -4701,22 +4819,21 @@
       <c r="C88" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E88" s="9"/>
       <c r="F88" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="J88" s="3"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>212</v>
       </c>
@@ -4730,683 +4847,732 @@
         <v>295</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>212</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E90" s="9"/>
+        <v>214</v>
+      </c>
+      <c r="E90" s="8"/>
       <c r="F90" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E91" s="9"/>
+        <v>214</v>
+      </c>
       <c r="F91" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>212</v>
       </c>
       <c r="B92" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>231</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="E92" s="8"/>
       <c r="F92" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>212</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>232</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="E93" s="8"/>
       <c r="F93" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>212</v>
       </c>
       <c r="B94" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H96" t="s">
-        <v>498</v>
+        <v>271</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>212</v>
       </c>
       <c r="B97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H97" t="s">
-        <v>499</v>
+        <v>272</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>212</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H98" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>212</v>
       </c>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H99" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H100" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H101" t="s">
-        <v>503</v>
-      </c>
-      <c r="I101" t="s">
-        <v>516</v>
+        <v>498</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>511</v>
       </c>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>212</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H102" t="s">
-        <v>504</v>
-      </c>
-      <c r="I102" t="s">
-        <v>517</v>
+        <v>499</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>212</v>
       </c>
       <c r="B103" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H103" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I103" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>212</v>
       </c>
       <c r="B104" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H104" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="I104" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>212</v>
       </c>
       <c r="B105" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>295</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H105" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="I105" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>212</v>
       </c>
       <c r="B106" t="s">
+        <v>250</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H106" t="s">
+        <v>503</v>
+      </c>
+      <c r="I106" t="s">
+        <v>517</v>
+      </c>
+      <c r="J106" s="3"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
+        <v>284</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H107" t="s">
+        <v>504</v>
+      </c>
+      <c r="I107" t="s">
+        <v>516</v>
+      </c>
+      <c r="J107" s="3"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" t="s">
         <v>283</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G106" s="2" t="s">
+      <c r="F108" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="H106" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J106" s="3"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F107" s="2"/>
-      <c r="J107" s="3"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H108" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>505</v>
+      </c>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F109" s="2"/>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D112" s="9"/>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D113" s="9"/>
+    <row r="113" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D114" s="9"/>
+    <row r="114" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D114" s="8"/>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D115" s="9"/>
+    <row r="115" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D115" s="8"/>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D116" s="8"/>
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D117" s="8"/>
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J122" s="3"/>
     </row>
-    <row r="123" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:10" x14ac:dyDescent="0.25">
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J155" s="3"/>
     </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J156" s="3"/>
     </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J157" s="3"/>
     </row>
-    <row r="158" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J158" s="3"/>
     </row>
-    <row r="159" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J159" s="3"/>
     </row>
-    <row r="160" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J160" s="3"/>
     </row>
-    <row r="161" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J161" s="3"/>
     </row>
-    <row r="162" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J189" s="3"/>
+    </row>
+    <row r="190" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J190" s="3"/>
+    </row>
+    <row r="191" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J191" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F661" xr:uid="{937213F6-6876-4084-AFDC-31539A17536A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F663" xr:uid="{937213F6-6876-4084-AFDC-31539A17536A}">
       <formula1>"ja,nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5417,2625 +5583,2709 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B971DBA-23FA-4290-8659-12FCAD44EC5E}">
-  <dimension ref="A1:L175"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L181"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="6"/>
       <c r="E2" s="3" t="s">
         <v>201</v>
       </c>
       <c r="J2" s="2"/>
-      <c r="K2" s="7"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>2016850</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="7"/>
       <c r="E3" s="3" t="s">
         <v>202</v>
       </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="8"/>
+      <c r="K3" s="7"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="3" t="s">
         <v>201</v>
       </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="7"/>
+      <c r="K4" s="6"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>296</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>296</v>
       </c>
       <c r="B6" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>10000</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="3" t="s">
         <v>201</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="6"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="3" t="s">
         <v>201</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="7"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>204</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>10000</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K9" s="8"/>
+      <c r="K9" s="7"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B10" t="s">
         <v>210</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="K10" s="8"/>
+      <c r="K10" s="7"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B11" t="s">
         <v>328</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D11" s="8"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K11" s="8"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>322</v>
       </c>
       <c r="B12" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7">
         <v>2</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="K12" s="8"/>
+      <c r="K12" s="7"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>322</v>
       </c>
       <c r="B13" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="K13" s="8"/>
+      <c r="K13" s="7"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>322</v>
       </c>
       <c r="B14" t="s">
         <v>328</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K14" s="8"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>331</v>
       </c>
       <c r="B15" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7">
         <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="K15" s="8"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>331</v>
       </c>
       <c r="B16" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D16" s="8"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="K16" s="8"/>
+      <c r="K16" s="7"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>331</v>
       </c>
       <c r="B17" t="s">
         <v>328</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="8"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K17" s="8"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>333</v>
       </c>
       <c r="B18" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7">
         <v>4</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>333</v>
       </c>
       <c r="B19" t="s">
         <v>210</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D19" s="8"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>333</v>
       </c>
       <c r="B20" t="s">
         <v>328</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>336</v>
       </c>
       <c r="B21" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7">
         <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>336</v>
       </c>
       <c r="B22" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>336</v>
       </c>
       <c r="B23" t="s">
         <v>328</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>337</v>
       </c>
       <c r="B24" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7">
         <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>337</v>
       </c>
       <c r="B25" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>337</v>
       </c>
       <c r="B26" t="s">
         <v>328</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>338</v>
       </c>
       <c r="B27" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7">
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>338</v>
       </c>
       <c r="B28" t="s">
         <v>210</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>338</v>
       </c>
       <c r="B29" t="s">
         <v>328</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>339</v>
       </c>
       <c r="B30" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8">
+      <c r="C30" s="7"/>
+      <c r="D30" s="7">
         <v>8</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>339</v>
       </c>
       <c r="B31" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>339</v>
       </c>
       <c r="B32" t="s">
         <v>328</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B33" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8">
+      <c r="C33" s="7"/>
+      <c r="D33" s="7">
         <v>9</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B34" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B35" t="s">
         <v>328</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>341</v>
       </c>
       <c r="B36" t="s">
         <v>204</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7">
         <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>341</v>
       </c>
       <c r="B37" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>341</v>
       </c>
       <c r="B38" t="s">
         <v>328</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B39" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8">
+      <c r="C39" s="7"/>
+      <c r="D39" s="7">
         <v>11</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B40" t="s">
         <v>210</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B41" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>456</v>
       </c>
       <c r="B42" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>12</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>456</v>
       </c>
       <c r="B43" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>456</v>
       </c>
       <c r="B44" t="s">
         <v>328</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B45" t="s">
         <v>204</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="7">
         <v>13</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B46" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B47" t="s">
         <v>328</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="B48" t="s">
         <v>204</v>
       </c>
-      <c r="D48" s="8">
-        <v>2</v>
+      <c r="C48" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="K48" s="8"/>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="B49" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="8">
-        <v>4000</v>
-      </c>
-      <c r="D49" s="8"/>
+      <c r="C49" s="6" t="s">
+        <v>293</v>
+      </c>
       <c r="E49" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="B50" t="s">
         <v>328</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D50" s="8"/>
       <c r="E50" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K50" s="8"/>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>352</v>
+        <v>545</v>
       </c>
       <c r="B51" t="s">
         <v>204</v>
       </c>
-      <c r="D51" s="8">
-        <v>3</v>
+      <c r="C51" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>352</v>
+        <v>545</v>
       </c>
       <c r="B52" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="8">
-        <v>4000</v>
-      </c>
-      <c r="D52" s="8"/>
+      <c r="C52" s="6" t="s">
+        <v>293</v>
+      </c>
       <c r="E52" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>352</v>
+        <v>545</v>
       </c>
       <c r="B53" t="s">
         <v>328</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D53" s="8"/>
       <c r="E53" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s">
         <v>204</v>
       </c>
-      <c r="D54" s="8">
-        <v>4</v>
+      <c r="D54" s="7">
+        <v>2</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="K54" s="7"/>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B55" t="s">
         <v>210</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="7">
         <v>4000</v>
       </c>
-      <c r="D55" s="8"/>
+      <c r="D55" s="7"/>
       <c r="E55" s="3" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K55" s="7"/>
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B56" t="s">
         <v>328</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D56" s="8"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="3" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K56" s="7"/>
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s">
         <v>204</v>
       </c>
-      <c r="D57" s="8">
-        <v>5</v>
+      <c r="D57" s="7">
+        <v>3</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B58" t="s">
         <v>210</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="7">
         <v>4000</v>
       </c>
+      <c r="D58" s="7"/>
       <c r="E58" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s">
         <v>328</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>329</v>
       </c>
+      <c r="D59" s="7"/>
       <c r="E59" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B60" t="s">
         <v>204</v>
       </c>
-      <c r="D60" s="8">
-        <v>6</v>
+      <c r="D60" s="7">
+        <v>4</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s">
         <v>210</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="7">
         <v>4000</v>
       </c>
+      <c r="D61" s="7"/>
       <c r="E61" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s">
         <v>328</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>329</v>
       </c>
+      <c r="D62" s="7"/>
       <c r="E62" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s">
         <v>204</v>
       </c>
-      <c r="D63" s="8">
-        <v>7</v>
+      <c r="D63" s="7">
+        <v>5</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s">
         <v>210</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="7">
         <v>4000</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B65" t="s">
         <v>328</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B66" t="s">
         <v>204</v>
       </c>
-      <c r="D66" s="8">
-        <v>8</v>
+      <c r="D66" s="7">
+        <v>6</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B67" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="7">
         <v>4000</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B69" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="8">
-        <v>9</v>
+      <c r="D69" s="7">
+        <v>7</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B70" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="7">
         <v>4000</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B71" t="s">
         <v>328</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B72" t="s">
         <v>204</v>
       </c>
-      <c r="D72" s="8">
-        <v>10</v>
+      <c r="D72" s="7">
+        <v>8</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B73" t="s">
         <v>210</v>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="7">
         <v>4000</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B74" t="s">
         <v>328</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B75" t="s">
         <v>204</v>
       </c>
-      <c r="D75" s="8">
-        <v>11</v>
+      <c r="D75" s="7">
+        <v>9</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B76" t="s">
         <v>210</v>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="7">
         <v>4000</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B77" t="s">
         <v>328</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="B78" t="s">
         <v>204</v>
       </c>
-      <c r="D78" s="8">
-        <v>12</v>
+      <c r="D78" s="7">
+        <v>10</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="B79" t="s">
         <v>210</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="7">
         <v>4000</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="B80" t="s">
         <v>328</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>461</v>
+        <v>360</v>
       </c>
       <c r="B81" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="8">
-        <v>13</v>
+      <c r="D81" s="7">
+        <v>11</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>461</v>
+        <v>360</v>
       </c>
       <c r="B82" t="s">
         <v>210</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="7">
         <v>4000</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>461</v>
+        <v>360</v>
       </c>
       <c r="B83" t="s">
         <v>328</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s">
         <v>204</v>
       </c>
-      <c r="D84" s="8">
-        <v>2</v>
+      <c r="D84" s="7">
+        <v>12</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s">
         <v>210</v>
       </c>
-      <c r="C85" s="8">
-        <v>3000</v>
-      </c>
-      <c r="D85" s="8"/>
+      <c r="C85" s="7">
+        <v>4000</v>
+      </c>
       <c r="E85" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>361</v>
+        <v>460</v>
       </c>
       <c r="B86" t="s">
         <v>328</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D86" s="8"/>
       <c r="E86" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>362</v>
+        <v>461</v>
       </c>
       <c r="B87" t="s">
         <v>204</v>
       </c>
-      <c r="D87" s="8">
-        <v>3</v>
+      <c r="D87" s="7">
+        <v>13</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>362</v>
+        <v>461</v>
       </c>
       <c r="B88" t="s">
         <v>210</v>
       </c>
-      <c r="C88" s="8">
-        <v>3000</v>
-      </c>
-      <c r="D88" s="8"/>
+      <c r="C88" s="7">
+        <v>4000</v>
+      </c>
       <c r="E88" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>362</v>
+        <v>461</v>
       </c>
       <c r="B89" t="s">
         <v>328</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D89" s="8"/>
       <c r="E89" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B90" t="s">
         <v>204</v>
       </c>
-      <c r="D90" s="8">
-        <v>4</v>
+      <c r="D90" s="7">
+        <v>2</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B91" t="s">
         <v>210</v>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="7">
         <v>3000</v>
       </c>
-      <c r="D91" s="8"/>
+      <c r="D91" s="7"/>
       <c r="E91" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B92" t="s">
         <v>328</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D92" s="8"/>
+      <c r="D92" s="7"/>
       <c r="E92" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B93" t="s">
         <v>204</v>
       </c>
-      <c r="D93" s="8">
-        <v>5</v>
+      <c r="D93" s="7">
+        <v>3</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B94" t="s">
         <v>210</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="7">
         <v>3000</v>
       </c>
+      <c r="D94" s="7"/>
       <c r="E94" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B95" t="s">
         <v>328</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="6" t="s">
         <v>329</v>
       </c>
+      <c r="D95" s="7"/>
       <c r="E95" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B96" t="s">
         <v>204</v>
       </c>
-      <c r="D96" s="8">
-        <v>6</v>
+      <c r="D96" s="7">
+        <v>4</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B97" t="s">
         <v>210</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="7">
         <v>3000</v>
       </c>
+      <c r="D97" s="7"/>
       <c r="E97" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B98" t="s">
         <v>328</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="6" t="s">
         <v>329</v>
       </c>
+      <c r="D98" s="7"/>
       <c r="E98" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B99" t="s">
         <v>204</v>
       </c>
-      <c r="D99" s="8">
-        <v>7</v>
+      <c r="D99" s="7">
+        <v>5</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B100" t="s">
         <v>210</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="7">
         <v>3000</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B101" t="s">
         <v>328</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B102" t="s">
         <v>204</v>
       </c>
-      <c r="D102" s="8">
-        <v>8</v>
+      <c r="D102" s="7">
+        <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B103" t="s">
         <v>210</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="7">
         <v>3000</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B104" t="s">
         <v>328</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B105" t="s">
         <v>204</v>
       </c>
-      <c r="D105" s="8">
-        <v>9</v>
+      <c r="D105" s="7">
+        <v>7</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B106" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="7">
         <v>3000</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B107" t="s">
         <v>328</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B108" t="s">
         <v>204</v>
       </c>
-      <c r="D108" s="8">
-        <v>10</v>
+      <c r="D108" s="7">
+        <v>8</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s">
         <v>210</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="7">
         <v>3000</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B110" t="s">
         <v>328</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B111" t="s">
         <v>204</v>
       </c>
-      <c r="D111" s="8">
-        <v>11</v>
+      <c r="D111" s="7">
+        <v>9</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B112" t="s">
         <v>210</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="7">
         <v>3000</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B113" t="s">
         <v>328</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>462</v>
+        <v>369</v>
       </c>
       <c r="B114" t="s">
         <v>204</v>
       </c>
-      <c r="D114" s="8">
-        <v>12</v>
+      <c r="D114" s="7">
+        <v>10</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>462</v>
+        <v>369</v>
       </c>
       <c r="B115" t="s">
         <v>210</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="7">
         <v>3000</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>462</v>
+        <v>369</v>
       </c>
       <c r="B116" t="s">
         <v>328</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>463</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s">
         <v>204</v>
       </c>
-      <c r="D117" s="8">
-        <v>13</v>
+      <c r="D117" s="7">
+        <v>11</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>463</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s">
         <v>210</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="7">
         <v>3000</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>463</v>
+        <v>370</v>
       </c>
       <c r="B119" t="s">
         <v>328</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C119" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>256</v>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="B120" t="s">
         <v>204</v>
       </c>
-      <c r="C120" s="8">
-        <v>10000</v>
+      <c r="D120" s="7">
+        <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>256</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="B121" t="s">
         <v>210</v>
       </c>
-      <c r="C121" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D121" s="8"/>
+      <c r="C121" s="7">
+        <v>3000</v>
+      </c>
       <c r="E121" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>257</v>
+        <v>462</v>
       </c>
       <c r="B122" t="s">
+        <v>328</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B123" t="s">
         <v>204</v>
       </c>
-      <c r="C122" s="8">
-        <v>41400</v>
-      </c>
-      <c r="D122" s="8"/>
-      <c r="E122" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="K122" s="8"/>
-      <c r="L122" s="3"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B123" t="s">
+      <c r="D123" s="7">
+        <v>13</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B124" t="s">
         <v>210</v>
       </c>
-      <c r="C123" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D123" s="8"/>
-      <c r="E123" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K123" s="8"/>
-      <c r="L123" s="3"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B124" t="s">
-        <v>204</v>
-      </c>
-      <c r="C124" s="8">
-        <v>60300</v>
-      </c>
-      <c r="D124" s="8"/>
+      <c r="C124" s="7">
+        <v>3000</v>
+      </c>
       <c r="E124" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K124" s="8"/>
-      <c r="L124" s="3"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>258</v>
+        <v>463</v>
       </c>
       <c r="B125" t="s">
-        <v>210</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D125" s="8"/>
+        <v>328</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>329</v>
+      </c>
       <c r="E125" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K125" s="8"/>
-      <c r="L125" s="3"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>259</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>256</v>
       </c>
       <c r="B126" t="s">
         <v>204</v>
       </c>
-      <c r="C126" s="8">
-        <v>60400</v>
-      </c>
-      <c r="D126" s="8"/>
+      <c r="C126" s="7">
+        <v>10000</v>
+      </c>
       <c r="E126" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="K126" s="8"/>
-      <c r="L126" s="3"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>259</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>256</v>
       </c>
       <c r="B127" t="s">
         <v>210</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D127" s="8"/>
+      <c r="D127" s="7"/>
       <c r="E127" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K127" s="8"/>
-      <c r="L127" s="3"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B128" t="s">
         <v>204</v>
       </c>
-      <c r="C128" s="8">
-        <v>60500</v>
-      </c>
-      <c r="D128" s="8"/>
+      <c r="C128" s="7">
+        <v>41400</v>
+      </c>
+      <c r="D128" s="7"/>
       <c r="E128" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K128" s="8"/>
+        <v>215</v>
+      </c>
+      <c r="K128" s="7"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B129" t="s">
         <v>210</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C129" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D129" s="8"/>
+      <c r="D129" s="7"/>
       <c r="E129" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K129" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K129" s="7"/>
       <c r="L129" s="3"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B130" t="s">
         <v>204</v>
       </c>
-      <c r="C130" s="8">
-        <v>60600</v>
-      </c>
-      <c r="D130" s="8"/>
+      <c r="C130" s="7">
+        <v>60300</v>
+      </c>
+      <c r="D130" s="7"/>
       <c r="E130" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K130" s="8"/>
+        <v>216</v>
+      </c>
+      <c r="K130" s="7"/>
       <c r="L130" s="3"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B131" t="s">
         <v>210</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="C131" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D131" s="8"/>
+      <c r="D131" s="7"/>
       <c r="E131" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K131" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K131" s="7"/>
       <c r="L131" s="3"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B132" t="s">
         <v>204</v>
       </c>
-      <c r="C132" s="8">
-        <v>60700</v>
-      </c>
-      <c r="D132" s="8"/>
+      <c r="C132" s="7">
+        <v>60400</v>
+      </c>
+      <c r="D132" s="7"/>
       <c r="E132" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="K132" s="8"/>
+        <v>217</v>
+      </c>
+      <c r="K132" s="7"/>
       <c r="L132" s="3"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B133" t="s">
         <v>210</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C133" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D133" s="8"/>
+      <c r="D133" s="7"/>
       <c r="E133" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K133" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K133" s="7"/>
       <c r="L133" s="3"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B134" t="s">
         <v>204</v>
       </c>
-      <c r="C134" s="8">
-        <v>60800</v>
-      </c>
-      <c r="D134" s="8"/>
+      <c r="C134" s="7">
+        <v>60500</v>
+      </c>
+      <c r="D134" s="7"/>
       <c r="E134" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="K134" s="8"/>
+        <v>218</v>
+      </c>
+      <c r="K134" s="7"/>
       <c r="L134" s="3"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B135" t="s">
         <v>210</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C135" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D135" s="8"/>
+      <c r="D135" s="7"/>
       <c r="E135" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K135" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K135" s="7"/>
       <c r="L135" s="3"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B136" t="s">
         <v>204</v>
       </c>
-      <c r="C136" s="8">
-        <v>21700</v>
-      </c>
-      <c r="D136" s="8"/>
+      <c r="C136" s="7">
+        <v>60600</v>
+      </c>
+      <c r="D136" s="7"/>
       <c r="E136" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K136" s="8"/>
+        <v>219</v>
+      </c>
+      <c r="K136" s="7"/>
       <c r="L136" s="3"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B137" t="s">
         <v>210</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C137" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D137" s="8"/>
+      <c r="D137" s="7"/>
       <c r="E137" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K137" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K137" s="7"/>
       <c r="L137" s="3"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B138" t="s">
         <v>204</v>
       </c>
-      <c r="C138" s="8">
-        <v>10000</v>
-      </c>
-      <c r="D138" s="8"/>
+      <c r="C138" s="7">
+        <v>60700</v>
+      </c>
+      <c r="D138" s="7"/>
       <c r="E138" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="K138" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="K138" s="7"/>
       <c r="L138" s="3"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B139" t="s">
         <v>210</v>
       </c>
-      <c r="C139" s="8">
-        <v>3000</v>
-      </c>
-      <c r="D139" s="8"/>
+      <c r="C139" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D139" s="7"/>
       <c r="E139" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K139" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K139" s="7"/>
       <c r="L139" s="3"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B140" t="s">
         <v>204</v>
       </c>
-      <c r="C140" s="8">
-        <v>10000</v>
-      </c>
-      <c r="D140" s="8"/>
+      <c r="C140" s="7">
+        <v>60800</v>
+      </c>
+      <c r="D140" s="7"/>
       <c r="E140" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="K140" s="8"/>
+        <v>221</v>
+      </c>
+      <c r="K140" s="7"/>
       <c r="L140" s="3"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B141" t="s">
         <v>210</v>
       </c>
-      <c r="C141" s="8">
-        <v>4000</v>
-      </c>
-      <c r="D141" s="8"/>
+      <c r="C141" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D141" s="7"/>
       <c r="E141" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K141" s="8"/>
+        <v>476</v>
+      </c>
+      <c r="K141" s="7"/>
       <c r="L141" s="3"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B142" t="s">
         <v>204</v>
       </c>
-      <c r="C142" s="8">
-        <v>10000</v>
-      </c>
+      <c r="C142" s="7">
+        <v>21700</v>
+      </c>
+      <c r="D142" s="7"/>
       <c r="E142" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="K142" s="7"/>
+      <c r="L142" s="3"/>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B143" t="s">
         <v>210</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D143" s="8"/>
+      <c r="D143" s="7"/>
       <c r="E143" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+      <c r="K143" s="7"/>
+      <c r="L143" s="3"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B144" t="s">
         <v>204</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="7">
         <v>10000</v>
       </c>
+      <c r="D144" s="7"/>
       <c r="E144" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+      <c r="K144" s="7"/>
+      <c r="L144" s="3"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B145" t="s">
         <v>210</v>
       </c>
-      <c r="C145" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D145" s="8"/>
+      <c r="C145" s="7">
+        <v>3000</v>
+      </c>
+      <c r="D145" s="7"/>
       <c r="E145" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="K145" s="7"/>
+      <c r="L145" s="3"/>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B146" t="s">
         <v>204</v>
       </c>
-      <c r="C146" s="8">
+      <c r="C146" s="7">
         <v>10000</v>
       </c>
+      <c r="D146" s="7"/>
       <c r="E146" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+      <c r="K146" s="7"/>
+      <c r="L146" s="3"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B147" t="s">
         <v>210</v>
       </c>
-      <c r="C147" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D147" s="8"/>
+      <c r="C147" s="7">
+        <v>4000</v>
+      </c>
+      <c r="D147" s="7"/>
       <c r="E147" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="K147" s="7"/>
+      <c r="L147" s="3"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B148" t="s">
         <v>204</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="7">
         <v>10000</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B149" t="s">
         <v>210</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C149" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D149" s="8"/>
+      <c r="D149" s="7"/>
       <c r="E149" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B150" t="s">
         <v>204</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="7">
         <v>10000</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B151" t="s">
         <v>210</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D151" s="8"/>
+      <c r="D151" s="7"/>
       <c r="E151" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B152" t="s">
         <v>204</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="7">
         <v>10000</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B153" t="s">
         <v>210</v>
       </c>
-      <c r="C153" s="7" t="s">
+      <c r="C153" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D153" s="8"/>
+      <c r="D153" s="7"/>
       <c r="E153" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B154" t="s">
         <v>204</v>
       </c>
-      <c r="C154" s="8">
+      <c r="C154" s="7">
         <v>10000</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B155" t="s">
         <v>210</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="C155" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D155" s="8"/>
+      <c r="D155" s="7"/>
       <c r="E155" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B156" t="s">
         <v>204</v>
       </c>
-      <c r="C156" s="8">
+      <c r="C156" s="7">
         <v>10000</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B157" t="s">
         <v>210</v>
       </c>
-      <c r="C157" s="7" t="s">
+      <c r="C157" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D157" s="8"/>
+      <c r="D157" s="7"/>
       <c r="E157" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B158" t="s">
         <v>204</v>
       </c>
-      <c r="C158" s="8">
+      <c r="C158" s="7">
         <v>10000</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B159" t="s">
         <v>210</v>
       </c>
-      <c r="C159" s="7" t="s">
+      <c r="C159" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D159" s="8"/>
+      <c r="D159" s="7"/>
       <c r="E159" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
         <v>204</v>
       </c>
-      <c r="C160" s="8">
+      <c r="C160" s="7">
         <v>10000</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B161" t="s">
         <v>210</v>
       </c>
-      <c r="C161" s="7" t="s">
+      <c r="C161" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D161" s="8"/>
+      <c r="D161" s="7"/>
       <c r="E161" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B162" t="s">
         <v>204</v>
       </c>
-      <c r="C162" s="8">
+      <c r="C162" s="7">
         <v>10000</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B163" t="s">
         <v>210</v>
       </c>
-      <c r="C163" s="7" t="s">
+      <c r="C163" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D163" s="8"/>
+      <c r="D163" s="7"/>
       <c r="E163" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B164" t="s">
         <v>204</v>
       </c>
-      <c r="C164" s="8">
+      <c r="C164" s="7">
         <v>10000</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B165" t="s">
         <v>210</v>
       </c>
-      <c r="C165" s="7" t="s">
+      <c r="C165" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D165" s="8"/>
+      <c r="D165" s="7"/>
       <c r="E165" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B166" t="s">
         <v>204</v>
       </c>
-      <c r="C166" s="8">
+      <c r="C166" s="7">
         <v>10000</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B167" t="s">
         <v>210</v>
       </c>
-      <c r="C167" s="7" t="s">
+      <c r="C167" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D167" s="8"/>
+      <c r="D167" s="7"/>
       <c r="E167" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B168" t="s">
         <v>204</v>
       </c>
-      <c r="C168" s="8">
+      <c r="C168" s="7">
         <v>10000</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B169" t="s">
         <v>210</v>
       </c>
-      <c r="C169" s="7" t="s">
+      <c r="C169" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D169" s="8"/>
+      <c r="D169" s="7"/>
       <c r="E169" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B170" t="s">
         <v>204</v>
       </c>
-      <c r="C170" s="8">
+      <c r="C170" s="7">
         <v>10000</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B171" t="s">
         <v>210</v>
       </c>
-      <c r="C171" s="7" t="s">
+      <c r="C171" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D171" s="8"/>
+      <c r="D171" s="7"/>
       <c r="E171" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B172" t="s">
         <v>204</v>
       </c>
-      <c r="C172" s="8">
+      <c r="C172" s="7">
         <v>10000</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B173" t="s">
         <v>210</v>
       </c>
-      <c r="C173" s="7" t="s">
+      <c r="C173" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D173" s="8"/>
+      <c r="D173" s="7"/>
       <c r="E173" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B174" t="s">
         <v>204</v>
       </c>
-      <c r="C174" s="8">
+      <c r="C174" s="7">
         <v>10000</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B175" t="s">
         <v>210</v>
       </c>
-      <c r="C175" s="7" t="s">
+      <c r="C175" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D175" s="8"/>
+      <c r="D175" s="7"/>
       <c r="E175" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B176" t="s">
+        <v>204</v>
+      </c>
+      <c r="C176" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B177" t="s">
+        <v>210</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D177" s="7"/>
+      <c r="E177" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B178" t="s">
+        <v>204</v>
+      </c>
+      <c r="C178" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B179" t="s">
+        <v>210</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D179" s="7"/>
+      <c r="E179" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B180" t="s">
+        <v>204</v>
+      </c>
+      <c r="C180" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B181" t="s">
+        <v>210</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D181" s="7"/>
+      <c r="E181" s="3" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -8045,38 +8295,38 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C088605-A26C-4C42-A4E5-A84C862CBB5B}">
-  <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.44140625" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.88671875" customWidth="1"/>
-    <col min="4" max="4" width="65.88671875" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" customWidth="1"/>
+    <col min="4" max="4" width="65.85546875" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>308</v>
       </c>
@@ -8098,7 +8348,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>309</v>
       </c>
@@ -8115,10 +8365,10 @@
         <v>315</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>310</v>
       </c>
@@ -8135,10 +8385,10 @@
         <v>315</v>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>311</v>
       </c>
@@ -8155,10 +8405,10 @@
         <v>315</v>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>312</v>
       </c>
@@ -8175,10 +8425,10 @@
         <v>315</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>313</v>
       </c>
@@ -8195,10 +8445,10 @@
         <v>315</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>390</v>
       </c>
@@ -8215,12 +8465,12 @@
         <v>315</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>391</v>
       </c>
@@ -8237,11 +8487,11 @@
         <v>315</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>392</v>
       </c>
@@ -8258,11 +8508,11 @@
         <v>315</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>393</v>
       </c>
@@ -8279,11 +8529,11 @@
         <v>315</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>394</v>
       </c>
@@ -8300,11 +8550,11 @@
         <v>315</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>395</v>
       </c>
@@ -8321,11 +8571,11 @@
         <v>315</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>396</v>
       </c>
@@ -8342,11 +8592,11 @@
         <v>315</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>397</v>
       </c>
@@ -8363,11 +8613,11 @@
         <v>315</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>398</v>
       </c>
@@ -8384,11 +8634,11 @@
         <v>315</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>399</v>
       </c>
@@ -8405,32 +8655,32 @@
         <v>315</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>478</v>
+        <v>577</v>
       </c>
       <c r="E18" t="s">
         <v>315</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>416</v>
       </c>
@@ -8447,10 +8697,10 @@
         <v>315</v>
       </c>
       <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>417</v>
       </c>
@@ -8467,10 +8717,10 @@
         <v>315</v>
       </c>
       <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>418</v>
       </c>
@@ -8487,10 +8737,10 @@
         <v>315</v>
       </c>
       <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>419</v>
       </c>
@@ -8507,10 +8757,10 @@
         <v>315</v>
       </c>
       <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>420</v>
       </c>
@@ -8527,10 +8777,10 @@
         <v>315</v>
       </c>
       <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>421</v>
       </c>
@@ -8547,10 +8797,10 @@
         <v>315</v>
       </c>
       <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>422</v>
       </c>
@@ -8567,10 +8817,10 @@
         <v>315</v>
       </c>
       <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>423</v>
       </c>
@@ -8587,10 +8837,10 @@
         <v>315</v>
       </c>
       <c r="F26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>424</v>
       </c>
@@ -8607,10 +8857,10 @@
         <v>315</v>
       </c>
       <c r="F27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>425</v>
       </c>
@@ -8627,30 +8877,30 @@
         <v>315</v>
       </c>
       <c r="F28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>475</v>
+        <v>576</v>
       </c>
       <c r="E29" t="s">
         <v>315</v>
       </c>
       <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>426</v>
       </c>
@@ -8667,10 +8917,10 @@
         <v>315</v>
       </c>
       <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>427</v>
       </c>
@@ -8687,10 +8937,10 @@
         <v>315</v>
       </c>
       <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>428</v>
       </c>
@@ -8707,10 +8957,10 @@
         <v>315</v>
       </c>
       <c r="F32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>429</v>
       </c>
@@ -8727,10 +8977,10 @@
         <v>315</v>
       </c>
       <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>430</v>
       </c>
@@ -8747,10 +8997,10 @@
         <v>315</v>
       </c>
       <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>431</v>
       </c>
@@ -8767,10 +9017,10 @@
         <v>315</v>
       </c>
       <c r="F35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>432</v>
       </c>
@@ -8787,10 +9037,10 @@
         <v>315</v>
       </c>
       <c r="F36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>433</v>
       </c>
@@ -8807,10 +9057,10 @@
         <v>315</v>
       </c>
       <c r="F37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>434</v>
       </c>
@@ -8827,10 +9077,10 @@
         <v>315</v>
       </c>
       <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>435</v>
       </c>
@@ -8847,27 +9097,267 @@
         <v>315</v>
       </c>
       <c r="F39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>470</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>471</v>
+        <v>575</v>
       </c>
       <c r="E40" t="s">
         <v>315</v>
       </c>
       <c r="F40">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D41" t="s">
+        <v>538</v>
+      </c>
+      <c r="E41" t="s">
+        <v>317</v>
+      </c>
+      <c r="F41">
         <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E42" t="s">
+        <v>317</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E44" t="s">
+        <v>317</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E45" t="s">
+        <v>315</v>
+      </c>
+      <c r="F45">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E46" t="s">
+        <v>317</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E47" t="s">
+        <v>315</v>
+      </c>
+      <c r="F47">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E50" t="s">
+        <v>315</v>
+      </c>
+      <c r="F50">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E51" t="s">
+        <v>315</v>
+      </c>
+      <c r="F51">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E52" t="s">
+        <v>315</v>
+      </c>
+      <c r="F52">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -8877,22 +9367,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8901,7 +9375,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4EA295FB1FB9547A73C9F5819D6E613" ma:contentTypeVersion="23" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fb09b8f9996d29818860aca561f17aea">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4e95bed8-6d15-4403-ad70-a53422338dca" xmlns:ns3="10d3344f-2d16-43d9-a145-97142f5cb288" xmlns:ns4="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f29125cba2118f3064d103e6e0ba85ce" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9186,27 +9660,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B2EDF01-6F7E-4DF9-9F88-B818D2B74C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="0655e6f0-bc5a-4a6f-90a0-f11d05f73b85"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c1decae3-bc71-419f-8045-b4e53679b539"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
-    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8069972A-8AC8-46B4-B83D-A93C29A0EF5A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -9214,7 +9684,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34C22BA0-1772-4802-A0A5-1C083BD3B5B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9233,4 +9703,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B2EDF01-6F7E-4DF9-9F88-B818D2B74C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="0655e6f0-bc5a-4a6f-90a0-f11d05f73b85"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c1decae3-bc71-419f-8045-b4e53679b539"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
+    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>